--- a/Hardware/BOM_Board1_PCB1_2026-03-07.xlsx
+++ b/Hardware/BOM_Board1_PCB1_2026-03-07.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0831C3AF-F597-4B0A-8AC8-2A5DC47509A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0338BB33-50C3-4A5B-B874-F1C99F5BC8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Board1_PCB1_2026-03-07" sheetId="1" r:id="rId1"/>
@@ -1787,14 +1787,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L79"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="30.75" customWidth="1"/>
+    <col min="5" max="5" width="30.7265625" customWidth="1"/>
     <col min="6" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>49</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>51</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>55</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>66</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>74</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>82</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>87</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>94</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>101</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>108</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>115</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>123</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>127</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>133</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>143</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>412</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>151</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>157</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>163</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>171</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>178</v>
       </c>
@@ -3048,14 +3048,14 @@
         <v>185</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B34" s="1">
         <v>5</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D34" t="s">
@@ -3086,7 +3086,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>190</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>193</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>196</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>204</v>
       </c>
@@ -3238,14 +3238,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B39" s="1">
         <v>10</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D39" t="s">
@@ -3276,7 +3276,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>211</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>214</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>217</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>220</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>223</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>226</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>229</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>231</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>234</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>237</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>398</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>243</v>
       </c>
@@ -3732,14 +3732,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D52" t="s">
@@ -3770,14 +3770,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B53" s="1">
         <v>2</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D53" t="s">
@@ -3808,7 +3808,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>399</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>259</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>263</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>400</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>410</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>401</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>288</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>293</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>301</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>402</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>403</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>404</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>324</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>405</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>334</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>342</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>346</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>354</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>360</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>365</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>372</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>379</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>386</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>391</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>406</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C79" t="s">
         <v>408</v>
       </c>
